--- a/Project/outputs/tables/table_gru_metrics_h5.xlsx
+++ b/Project/outputs/tables/table_gru_metrics_h5.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003080071415752172</v>
+        <v>0.003101208945736289</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03093661367893219</v>
+        <v>0.03048533387482166</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05549839110958238</v>
+        <v>0.05568849922323539</v>
       </c>
       <c r="E2" t="n">
-        <v>17.72463989257812</v>
+        <v>15.76552581787109</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001665796153247356</v>
+        <v>0.002010258147493005</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02636558376252651</v>
+        <v>0.03055423684418201</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04081416608540907</v>
+        <v>0.04483590243870424</v>
       </c>
       <c r="E3" t="n">
-        <v>18.31033325195312</v>
+        <v>17.88376045227051</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4526515151515151</v>
+        <v>0.4715909090909091</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002016030251979828</v>
+        <v>0.002090666675940156</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03042865730822086</v>
+        <v>0.03252534568309784</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04490022552259429</v>
+        <v>0.04572380863336032</v>
       </c>
       <c r="E4" t="n">
-        <v>17.32170295715332</v>
+        <v>20.95596504211426</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5037878787878788</v>
+        <v>0.4962121212121212</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001752196927554905</v>
+        <v>0.001973431091755629</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02768819406628609</v>
+        <v>0.03145068511366844</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04185925139744983</v>
+        <v>0.04442331698281465</v>
       </c>
       <c r="E5" t="n">
-        <v>16.6701488494873</v>
+        <v>18.30345153808594</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4753787878787879</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001227009459398687</v>
+        <v>0.001482439925894141</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02486809156835079</v>
+        <v>0.0268566906452179</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03502869480010191</v>
+        <v>0.03850246649104627</v>
       </c>
       <c r="E6" t="n">
-        <v>13.28420448303223</v>
+        <v>15.21714305877686</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4886363636363636</v>
+        <v>0.4981060606060606</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001475712051615119</v>
+        <v>0.001264663645997643</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02743138372898102</v>
+        <v>0.02387627214193344</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03841499774326583</v>
+        <v>0.03556210969554033</v>
       </c>
       <c r="E7" t="n">
-        <v>14.00802707672119</v>
+        <v>13.9050350189209</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4810606060606061</v>
+        <v>0.4734848484848485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003362427232787013</v>
+        <v>0.001894396264106035</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03827359527349472</v>
+        <v>0.03248924389481544</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05798644007685774</v>
+        <v>0.0435246627109968</v>
       </c>
       <c r="E8" t="n">
-        <v>17.81386566162109</v>
+        <v>15.4384937286377</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4640151515151515</v>
+        <v>0.4962121212121212</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001141325919888914</v>
+        <v>0.001013910863548517</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02298193797469139</v>
+        <v>0.02127614244818687</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0337835155051826</v>
+        <v>0.03184196701757788</v>
       </c>
       <c r="E9" t="n">
-        <v>12.07613754272461</v>
+        <v>13.73044109344482</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5227272727272727</v>
+        <v>0.5265151515151515</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001965071176527999</v>
+        <v>0.001853871945058927</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02862175717018545</v>
+        <v>0.02868924383074045</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04353571028005546</v>
+        <v>0.04251284164915949</v>
       </c>
       <c r="E10" t="n">
-        <v>15.90113258361816</v>
+        <v>16.39997673034668</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4808238636363636</v>
+        <v>0.4952651515151515</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.000952899397816509</v>
+        <v>0.002578736515715718</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01945338025689125</v>
+        <v>0.03819279745221138</v>
       </c>
       <c r="D11" t="n">
-        <v>0.030869068625673</v>
+        <v>0.05078126146243039</v>
       </c>
       <c r="E11" t="n">
-        <v>12.12384033203125</v>
+        <v>21.68354034423828</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5280748663101604</v>
+        <v>0.5355704697986577</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0007408247911371291</v>
+        <v>0.0008498640381731093</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01735803857445717</v>
+        <v>0.01995181478559971</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02721809675817045</v>
+        <v>0.02915242765488166</v>
       </c>
       <c r="E12" t="n">
-        <v>14.23557090759277</v>
+        <v>14.27613353729248</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4946524064171123</v>
+        <v>0.5167785234899329</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0007847939268685877</v>
+        <v>0.0008219829760491848</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01866152323782444</v>
+        <v>0.02089128270745277</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02801417367813279</v>
+        <v>0.02867024548289018</v>
       </c>
       <c r="E13" t="n">
-        <v>18.38393211364746</v>
+        <v>15.5135555267334</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4933155080213903</v>
+        <v>0.5167785234899329</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0009878696873784065</v>
+        <v>0.0007390471873804927</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02092723548412323</v>
+        <v>0.01905436627566814</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0314303943242589</v>
+        <v>0.02718542233220762</v>
       </c>
       <c r="E14" t="n">
-        <v>15.04996681213379</v>
+        <v>18.15773391723633</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4986631016042781</v>
+        <v>0.4899328859060403</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.003305475693196058</v>
+        <v>0.003443458350375295</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02769478410482407</v>
+        <v>0.03278102353215218</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05749326650309633</v>
+        <v>0.05868098798056569</v>
       </c>
       <c r="E15" t="n">
-        <v>12.98889827728271</v>
+        <v>16.00101280212402</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5006711409395973</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.00270276446826756</v>
+        <v>0.001662216964177787</v>
       </c>
       <c r="C16" t="n">
-        <v>0.03038138523697853</v>
+        <v>0.02578100748360157</v>
       </c>
       <c r="D16" t="n">
-        <v>0.05198811852979063</v>
+        <v>0.04077029512007225</v>
       </c>
       <c r="E16" t="n">
-        <v>12.55419254302979</v>
+        <v>14.17728519439697</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5187165775401069</v>
+        <v>0.5248322147651007</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.002156321192160249</v>
+        <v>0.004079814068973064</v>
       </c>
       <c r="C17" t="n">
-        <v>0.03258005529642105</v>
+        <v>0.04592655226588249</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0464362056176024</v>
+        <v>0.06387342224253421</v>
       </c>
       <c r="E17" t="n">
-        <v>19.39422607421875</v>
+        <v>18.5767650604248</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4692513368983957</v>
+        <v>0.5342281879194631</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.001256780931726098</v>
+        <v>0.001503532868809998</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02071272395551205</v>
+        <v>0.02608454786241055</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03545110621300974</v>
+        <v>0.03877541577868635</v>
       </c>
       <c r="E18" t="n">
-        <v>14.62008380889893</v>
+        <v>20.37861633300781</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5093582887700535</v>
+        <v>0.4724832214765101</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.001610966261068825</v>
+        <v>0.001959831621206831</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02347114076837897</v>
+        <v>0.02858292404562235</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03861255378121678</v>
+        <v>0.04223618475678354</v>
       </c>
       <c r="E19" t="n">
-        <v>14.91883850097656</v>
+        <v>17.3455810546875</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5051804812834224</v>
+        <v>0.5114093959731545</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
